--- a/vbt_bist/academic/output/Sektor_Strateji_Haritasi.xlsx
+++ b/vbt_bist/academic/output/Sektor_Strateji_Haritasi.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,54 +417,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Sektor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Diger</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Hacim</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Har. Ort.</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Momentum</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Mum</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ort. Donus</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Volatilite</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Banka</t>
         </is>
@@ -507,7 +495,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Cimento</t>
         </is>
@@ -538,7 +526,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Elektronik</t>
         </is>
@@ -569,7 +557,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Enerji</t>
         </is>
@@ -600,7 +588,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Finans</t>
         </is>
@@ -631,7 +619,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>GYO</t>
         </is>
@@ -662,7 +650,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Gida</t>
         </is>
@@ -693,7 +681,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -724,7 +712,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Ilac</t>
         </is>
@@ -755,7 +743,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Insaat</t>
         </is>
@@ -786,7 +774,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Kimya</t>
         </is>
@@ -817,7 +805,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Madencilik</t>
         </is>
@@ -848,7 +836,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Metal</t>
         </is>
@@ -879,7 +867,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Otomotiv</t>
         </is>
@@ -910,7 +898,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Perakende</t>
         </is>
@@ -941,7 +929,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Petrokimya</t>
         </is>
@@ -972,7 +960,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Sanayi</t>
         </is>
@@ -1003,7 +991,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Savunma</t>
         </is>
@@ -1034,7 +1022,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Sigorta</t>
         </is>
@@ -1065,7 +1053,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Tarim</t>
         </is>
@@ -1096,7 +1084,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
@@ -1127,7 +1115,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Tekstil</t>
         </is>
@@ -1158,7 +1146,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Telekom</t>
         </is>
@@ -1189,7 +1177,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Ulasim</t>
         </is>
